--- a/FinanceData.xlsx
+++ b/FinanceData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Data Analytics\Finance analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35F73370-96B8-4064-A60E-7D71C33796D7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE603769-1BE3-4A96-BB16-655711D85798}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8250" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="179021"/>
   <pivotCaches>
-    <pivotCache cacheId="13" r:id="rId4"/>
+    <pivotCache cacheId="19" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="37">
   <si>
     <t>Month</t>
   </si>
@@ -154,9 +154,6 @@
   </si>
   <si>
     <t>Sum of Expenses</t>
-  </si>
-  <si>
-    <t>insurance</t>
   </si>
 </sst>
 </file>
@@ -2790,7 +2787,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000E-DD6D-4D69-8A07-7F8752FCA880}"/>
+              <c16:uniqueId val="{0000000F-DD6D-4D69-8A07-7F8752FCA880}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2955,6 +2952,599 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[FinanceData.xlsx]Pivot tables!PivotTable13</c:name>
+    <c:fmtId val="6"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Product-wise</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> Profit</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent2">
+                  <a:tint val="50000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="35000">
+                <a:schemeClr val="accent2">
+                  <a:tint val="37000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent2">
+                  <a:tint val="15000"/>
+                  <a:satMod val="350000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="1"/>
+          </a:gradFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:shade val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:tint val="50000"/>
+                    <a:satMod val="300000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="35000">
+                  <a:schemeClr val="accent2">
+                    <a:tint val="37000"/>
+                    <a:satMod val="300000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:tint val="15000"/>
+                    <a:satMod val="350000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="1"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="38000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent2">
+                  <a:tint val="50000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="35000">
+                <a:schemeClr val="accent2">
+                  <a:tint val="37000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent2">
+                  <a:tint val="15000"/>
+                  <a:satMod val="350000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="1"/>
+          </a:gradFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:shade val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent2">
+                  <a:tint val="50000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="35000">
+                <a:schemeClr val="accent2">
+                  <a:tint val="37000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent2">
+                  <a:tint val="15000"/>
+                  <a:satMod val="350000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="1"/>
+          </a:gradFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:shade val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Pivot tables'!$J$34</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:tint val="50000"/>
+                    <a:satMod val="300000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="35000">
+                  <a:schemeClr val="accent2">
+                    <a:tint val="37000"/>
+                    <a:satMod val="300000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:tint val="15000"/>
+                    <a:satMod val="350000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="1"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="38000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pivot tables'!$I$35:$I$38</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Credit Card</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Insurance</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Loan</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pivot tables'!$J$35:$J$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2655301</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2501555</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3056536</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-09B0-42A6-9B3E-73A4A4963DCB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
+        <c:axId val="927841336"/>
+        <c:axId val="927840680"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="927841336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927840680"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="927840680"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927841336"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5181,7 +5771,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000E-3254-446E-B8FD-26E0ABEA8152}"/>
+              <c16:uniqueId val="{0000000F-3254-446E-B8FD-26E0ABEA8152}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5859,6 +6449,465 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
+    <c:name>[FinanceData.xlsx]Pivot tables!PivotTable13</c:name>
+    <c:fmtId val="4"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent2">
+                  <a:tint val="50000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="35000">
+                <a:schemeClr val="accent2">
+                  <a:tint val="37000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent2">
+                  <a:tint val="15000"/>
+                  <a:satMod val="350000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="1"/>
+          </a:gradFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:shade val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:tint val="50000"/>
+                    <a:satMod val="300000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="35000">
+                  <a:schemeClr val="accent2">
+                    <a:tint val="37000"/>
+                    <a:satMod val="300000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:tint val="15000"/>
+                    <a:satMod val="350000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="1"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="38000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Pivot tables'!$J$34</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:tint val="50000"/>
+                    <a:satMod val="300000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="35000">
+                  <a:schemeClr val="accent2">
+                    <a:tint val="37000"/>
+                    <a:satMod val="300000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:tint val="15000"/>
+                    <a:satMod val="350000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="1"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="38000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pivot tables'!$I$35:$I$38</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Credit Card</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Insurance</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Loan</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pivot tables'!$J$35:$J$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2655301</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2501555</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3056536</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-14FA-4F92-BD58-07A255A2CF6D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
+        <c:axId val="927841336"/>
+        <c:axId val="927840680"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="927841336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927840680"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="927840680"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927841336"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
     <c:name>[FinanceData.xlsx]Pivot tables!PivotTable1</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
@@ -6396,7 +7445,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7160,599 +8209,6 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[FinanceData.xlsx]Pivot tables!PivotTable2</c:name>
-    <c:fmtId val="3"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="50000"/>
-                    <a:lumOff val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200" b="1">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Product-wise</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t> Revenue</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent2">
-                  <a:tint val="50000"/>
-                  <a:satMod val="300000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="35000">
-                <a:schemeClr val="accent2">
-                  <a:tint val="37000"/>
-                  <a:satMod val="300000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent2">
-                  <a:tint val="15000"/>
-                  <a:satMod val="350000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="16200000" scaled="1"/>
-          </a:gradFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:shade val="95000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="4"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent2">
-                    <a:tint val="50000"/>
-                    <a:satMod val="300000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="35000">
-                  <a:schemeClr val="accent2">
-                    <a:tint val="37000"/>
-                    <a:satMod val="300000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent2">
-                    <a:tint val="15000"/>
-                    <a:satMod val="350000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="16200000" scaled="1"/>
-            </a:gradFill>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:shade val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="38000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-        </c:marker>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent2">
-                  <a:tint val="50000"/>
-                  <a:satMod val="300000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="35000">
-                <a:schemeClr val="accent2">
-                  <a:tint val="37000"/>
-                  <a:satMod val="300000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent2">
-                  <a:tint val="15000"/>
-                  <a:satMod val="350000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="16200000" scaled="1"/>
-          </a:gradFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:shade val="95000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent2">
-                  <a:tint val="50000"/>
-                  <a:satMod val="300000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="35000">
-                <a:schemeClr val="accent2">
-                  <a:tint val="37000"/>
-                  <a:satMod val="300000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent2">
-                  <a:tint val="15000"/>
-                  <a:satMod val="350000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="16200000" scaled="1"/>
-          </a:gradFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:shade val="95000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Pivot tables'!$B$12</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent2">
-                    <a:tint val="50000"/>
-                    <a:satMod val="300000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="35000">
-                  <a:schemeClr val="accent2">
-                    <a:tint val="37000"/>
-                    <a:satMod val="300000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent2">
-                    <a:tint val="15000"/>
-                    <a:satMod val="350000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="16200000" scaled="1"/>
-            </a:gradFill>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:shade val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="38000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pivot tables'!$A$13:$A$16</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Credit Card</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Insurance</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Loan</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Pivot tables'!$B$13:$B$16</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>5910353</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6306779</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6586249</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-04BD-4F5F-8F9C-A7A58B1343EC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
-        <c:axId val="847979696"/>
-        <c:axId val="847981336"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="847979696"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="50000"/>
-                    <a:lumOff val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="847981336"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="847981336"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="50000"/>
-                    <a:lumOff val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="847979696"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
   <a:schemeClr val="accent2"/>
@@ -7805,6 +8261,43 @@
 <file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
   <a:schemeClr val="accent2"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -10034,6 +10527,531 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="206">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="15875" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="293">
   <cs:axisTitle>
@@ -12634,6 +13652,531 @@
 </file>
 
 <file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="206">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="15875" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="293">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -13186,7 +14729,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="342">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -13683,531 +15226,6 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="301">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" cap="all"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="1"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:shade val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="1"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:shade val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="1"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="15875" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="1"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:shade val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -14486,6 +15504,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>374649</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>63499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>149224</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="16" name="Chart 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4907C6F5-048A-4BD4-953F-AF67ADE9AB27}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -15370,44 +16424,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>441854</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>170089</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>10585</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>42333</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="23" name="Chart 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54332295-F86C-443D-83F5-D746AAF2E13D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>42334</xdr:colOff>
       <xdr:row>11</xdr:row>
@@ -15438,7 +16454,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -15476,7 +16492,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -15514,7 +16530,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -16292,13 +17308,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId12"/>
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId11"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -16410,7 +17426,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -16454,13 +17470,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId15"/>
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId14"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -16572,7 +17588,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -16616,7 +17632,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -16641,7 +17657,7 @@
       <xdr:rowOff>162478</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1784047" cy="745874"/>
-    <xdr:sp macro="" textlink="Finance_Data!N10">
+    <xdr:sp macro="" textlink="'Pivot tables'!B21">
       <xdr:nvSpPr>
         <xdr:cNvPr id="49" name="TextBox 48">
           <a:extLst>
@@ -16682,7 +17698,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:fld id="{9E9C810C-99B4-4043-BDB8-540BD98E55FE}" type="TxLink">
+          <a:fld id="{F62F7A49-9E6B-4687-834B-C8DB91B9AAF0}" type="TxLink">
             <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
@@ -16725,7 +17741,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -16769,13 +17785,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId20"/>
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId19"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -16822,13 +17838,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId22"/>
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId21"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -16875,13 +17891,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId24"/>
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId23"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -16928,7 +17944,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -16943,6 +17959,44 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>424216</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>10080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>574524</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>30238</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="59" name="Chart 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26913AB9-BA51-4EB7-A1B0-23C954B2AB8A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -19041,7 +20095,85 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{427879A0-EDA2-41A0-AFD5-CEDB09CE3303}" name="PivotTable7" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{07DDB29A-D726-4A9C-9ED8-FCF2EF4295D6}" name="PivotTable13" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="I34:J38" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Profit" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="4" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{427879A0-EDA2-41A0-AFD5-CEDB09CE3303}" name="PivotTable7" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A42:B46" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -19126,8 +20258,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{44B255E6-D486-4DD7-AE02-30A204F650A8}" name="PivotTable5" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{44B255E6-D486-4DD7-AE02-30A204F650A8}" name="PivotTable5" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="I17:N31" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField axis="axisRow" showAll="0">
@@ -19343,8 +20475,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2CD38E86-2E5B-4F1B-921D-CDFCBD2DB123}" name="PivotTable4" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2CD38E86-2E5B-4F1B-921D-CDFCBD2DB123}" name="PivotTable4" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A25:B38" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField axis="axisRow" showAll="0">
@@ -19465,8 +20597,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E09E8D50-470E-432C-840D-B337133AFA7A}" name="PivotTable3" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E09E8D50-470E-432C-840D-B337133AFA7A}" name="PivotTable3" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="I1:J14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField axis="axisRow" showAll="0">
@@ -19587,8 +20719,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E1490B9D-A23F-4850-A1BB-B66A8F58DDA2}" name="PivotTable2" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E1490B9D-A23F-4850-A1BB-B66A8F58DDA2}" name="PivotTable2" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A12:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -19821,8 +20953,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AE53940E-0783-4495-9DD3-37EA4CB24F2F}" name="PivotTable1" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AE53940E-0783-4495-9DD3-37EA4CB24F2F}" name="PivotTable1" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A1:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -20828,10 +21960,6 @@
       <c r="K15">
         <v>2</v>
       </c>
-      <c r="N15">
-        <f>SUM(E3:E144)</f>
-        <v>10354013</v>
-      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -20866,13 +21994,6 @@
       </c>
       <c r="K16">
         <v>0</v>
-      </c>
-      <c r="M16" t="s">
-        <v>37</v>
-      </c>
-      <c r="N16">
-        <f>SUM(E4:E145)</f>
-        <v>10360983</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
@@ -25653,6 +26774,10 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B20">
+        <f>GETPIVOTDATA("Profit",$A$25)/GETPIVOTDATA("Revenue",$A$12)*100</f>
+        <v>43.680399817458358</v>
+      </c>
       <c r="I20" s="3" t="s">
         <v>20</v>
       </c>
@@ -25673,6 +26798,10 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B21">
+        <f>ROUNDUP(B20,2)</f>
+        <v>43.69</v>
+      </c>
       <c r="I21" s="3" t="s">
         <v>21</v>
       </c>
@@ -25957,6 +27086,12 @@
       <c r="B34" s="4">
         <v>855527</v>
       </c>
+      <c r="I34" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J34" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
@@ -25965,6 +27100,12 @@
       <c r="B35" s="4">
         <v>457403</v>
       </c>
+      <c r="I35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J35" s="4">
+        <v>2655301</v>
+      </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
@@ -25973,6 +27114,12 @@
       <c r="B36" s="4">
         <v>405634</v>
       </c>
+      <c r="I36" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="4">
+        <v>2501555</v>
+      </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
@@ -25981,12 +27128,24 @@
       <c r="B37" s="4">
         <v>711849</v>
       </c>
+      <c r="I37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J37" s="4">
+        <v>3056536</v>
+      </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B38" s="4">
+        <v>8213392</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J38" s="4">
         <v>8213392</v>
       </c>
     </row>
@@ -26011,10 +27170,6 @@
       <c r="B43" s="4">
         <v>3255052</v>
       </c>
-      <c r="J43">
-        <f>SUM(A31:A172)</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
@@ -26042,7 +27197,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId7"/>
+  <drawing r:id="rId8"/>
 </worksheet>
 </file>
 
